--- a/サーブレット.xlsx
+++ b/サーブレット.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g03582\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0263DA2B-8B72-400C-8D50-EC1FFFFFF82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401295CC-7678-4219-BEAA-D3EAAC810645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6F8A607D-92D3-4F30-9FE5-8F0305DB5A31}"/>
   </bookViews>
@@ -38,9 +38,124 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Java Servlet：Webサーバ上でお仕事をするJavaのプログラムのこと。またはその技術のこと。</t>
+    <rPh sb="46" eb="48">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spring Boot ／JSPといった、HTMLに対して、動的情報を掲示する技術の裏ではこのServletが動いている</t>
+    <rPh sb="26" eb="27">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ドウテキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケイジ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結局何がうれしいの？</t>
+    <rPh sb="0" eb="3">
+      <t>ケッキョクナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　→登場以前はサーバーサイドでの受付のルールが統一されていなかった。</t>
+    <rPh sb="2" eb="6">
+      <t>トウジョウイゼン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ウケツケ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウイツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セッション管理</t>
+  </si>
+  <si>
+    <t>URL とサーブレットの紐づけ</t>
+  </si>
+  <si>
+    <t>サーブレットのライフサイクル管理（生成・初期化・破棄）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 役割 ▼</t>
+    <rPh sb="1" eb="3">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スレッド管理（高速処理の要）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tomcat：Java Servlet を動かすソフト。Webコンテナ（サーブレットコンテナ）  のこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webコンテナとは：Java の Web アプリ（Servlet / JSP）を動かすための実行環境</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webコンテナの役割</t>
+    <rPh sb="8" eb="10">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・リクエスト受付 URL にアクセスされたら最初に受け取る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・Servlet のライフサイクル管理 生成 → 初期化 → 処理 → 破棄 を自動でやる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スレッド管理 同時アクセスを並列処理して高速化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Apache ：静的webページを届けるのに</t>
+    <rPh sb="8" eb="10">
+      <t>セイテキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>トド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,6 +168,23 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -79,8 +211,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -105,22 +243,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>90611</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>534336</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>67050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{401C85DF-22DC-11B1-67AA-ADBE66E9A3D0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F85444A-4ADF-D8BE-2B89-8D36876581FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -136,12 +274,17 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683560" y="1176618"/>
-          <a:ext cx="4784911" cy="2443846"/>
+          <a:off x="680357" y="489857"/>
+          <a:ext cx="6657550" cy="2761264"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -466,11 +609,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A39934E-D56B-4278-B2B9-5729874B5739}">
-  <dimension ref="A1"/>
+  <dimension ref="B20:L36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="C25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="L30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/サーブレット.xlsx
+++ b/サーブレット.xlsx
@@ -1,35 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g03582\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401295CC-7678-4219-BEAA-D3EAAC810645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2187C194-93DD-46F3-9786-50D64F5DB0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6F8A607D-92D3-4F30-9FE5-8F0305DB5A31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6F8A607D-92D3-4F30-9FE5-8F0305DB5A31}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="概要" sheetId="1" r:id="rId1"/>
+    <sheet name="公式ドキュメント" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -39,39 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Java Servlet：Webサーバ上でお仕事をするJavaのプログラムのこと。またはその技術のこと。</t>
-    <rPh sb="46" eb="48">
-      <t>ギジュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Spring Boot ／JSPといった、HTMLに対して、動的情報を掲示する技術の裏ではこのServletが動いている</t>
-    <rPh sb="26" eb="27">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ドウテキ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ケイジ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ウラ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>結局何がうれしいの？</t>
     <rPh sb="0" eb="3">
@@ -80,19 +38,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　→登場以前はサーバーサイドでの受付のルールが統一されていなかった。</t>
-    <rPh sb="2" eb="6">
-      <t>トウジョウイゼン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ウケツケ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>トウイツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>セッション管理</t>
   </si>
   <si>
@@ -114,14 +59,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Tomcat：Java Servlet を動かすソフト。Webコンテナ（サーブレットコンテナ）  のこと</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Webコンテナとは：Java の Web アプリ（Servlet / JSP）を動かすための実行環境</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Webコンテナの役割</t>
     <rPh sb="8" eb="10">
       <t>ヤクワリ</t>
@@ -141,21 +78,171 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Apache ：静的webページを届けるのに</t>
-    <rPh sb="8" eb="10">
-      <t>セイテキ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>トド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+    <t>Java Servletってなーに？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　⇒Webサーバ上でお仕事をするJavaのプログラムのこと。またはその技術のこと。</t>
+    <rPh sb="35" eb="37">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　・登場以前はサーバーサイドでの受付のルールが統一されていなかった。</t>
+    <rPh sb="2" eb="6">
+      <t>トウジョウイゼン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ウケツケ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウイツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　・標準化されたことによって、Spring Boot ／JSPといった、HTMLに対して、動的情報を掲示する技術の裏ではこのServletが動いている</t>
+    <rPh sb="2" eb="5">
+      <t>ヒョウジュンカ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ドウテキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ケイジ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CGIとは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　CGI（Common Gateway Interface）とは「Web サーバが外部プログラムを実行して、その結果をブラウザに返すための仕組み」です</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　・OSを選ばないでも、動作できるようになったよ。CGIで動かしていた当時は大変やったんや。。。。</t>
+    <rPh sb="5" eb="6">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トウジ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>タイヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　⇒Java Servlet を動かすソフト。Webコンテナ（サーブレットコンテナ）  のこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tomcatってなーに？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webコンテナってなーに？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　⇒Java の Web アプリ（Servlet / JSP）を動かすための実行環境</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Apacheってなーに？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　⇒HTML、CSS、画像などの 静的ファイルを高速に返すよ！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Apache君＞</t>
+    <rPh sb="6" eb="7">
+      <t>キミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　・開発者がそこまで開発環境の構成を意識しなくてもよくなったよ</t>
+    <rPh sb="2" eb="5">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補足</t>
+    <rPh sb="0" eb="2">
+      <t>ホソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参考：https://qiita.com/tanayasu1228/items/11e22a18dbfa796745b5</t>
+    <rPh sb="0" eb="2">
+      <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://tomcat.apache.org/tomcat-9.0-doc/architecture/</t>
+  </si>
+  <si>
+    <t>アーキテクチャについての公式</t>
+    <rPh sb="12" eb="14">
+      <t>コウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライフサイクルについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://tomcat.apache.org/tomcat-9.0-doc/api/org/apache/catalina/Lifecycle.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +275,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -197,7 +293,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -205,13 +301,96 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -221,8 +400,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -240,25 +456,205 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>620486</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>175531</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2722</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>72132</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="グループ化 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF617BED-3DEF-D759-3AB6-5C91A95F1453}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="620486" y="413656"/>
+          <a:ext cx="4868636" cy="2754101"/>
+          <a:chOff x="8001000" y="1034143"/>
+          <a:chExt cx="4830536" cy="2824858"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="2" name="図 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD760D9B-6203-3E51-4440-C9B5168AA5D3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="10164536" y="1215117"/>
+            <a:ext cx="2667000" cy="2643884"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="吹き出し: 角を丸めた四角形 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3339078A-C6C6-2A1A-1BB5-3B2A1B69FFBB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8001000" y="1034143"/>
+            <a:ext cx="2490107" cy="1455964"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 62009"/>
+              <a:gd name="adj2" fmla="val 42913"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>サーブレット、サーブレットといいますが、意味が分かりません。</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>何ですか？サーブレットって？</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>お菓子ですか？</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>534336</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>67050</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>191135</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F85444A-4ADF-D8BE-2B89-8D36876581FB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A842BFB-C183-8F0B-C877-AF45643BD8CD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -267,15 +663,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="680357" y="489857"/>
-          <a:ext cx="6657550" cy="2761264"/>
+          <a:off x="683559" y="3529853"/>
+          <a:ext cx="5468470" cy="3956311"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -287,6 +683,233 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>156883</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>612579</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>187137</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="11" name="グループ化 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B9CBB9F-D557-E8D1-D562-BE0331CBB98E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2900083" y="13096875"/>
+          <a:ext cx="7999496" cy="3768537"/>
+          <a:chOff x="2900083" y="13096875"/>
+          <a:chExt cx="7999496" cy="3768537"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="9" name="グループ化 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E29B78BC-C8BE-E2A7-8E5B-33BCEA7B85D9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2900083" y="13274487"/>
+            <a:ext cx="5957046" cy="3590925"/>
+            <a:chOff x="2891118" y="13334999"/>
+            <a:chExt cx="5939117" cy="3548903"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="7" name="図 6" descr="ブラック企業のイラスト">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CC5CCFE-A31D-319B-86EF-970AC47BB6E9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="5031441" y="13334999"/>
+              <a:ext cx="3798794" cy="3548903"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="吹き出し: 角を丸めた四角形 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F4D0363-DF2B-406D-AF27-DB539CAAB7CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2891118" y="13738412"/>
+              <a:ext cx="2500505" cy="952500"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRoundRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 62009"/>
+                <a:gd name="adj2" fmla="val 42913"/>
+                <a:gd name="adj3" fmla="val 16667"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>動的ウェブページを返すのは得意じゃないから、あとはサーブレット君に任せよう</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="吹き出し: 角を丸めた四角形 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A30E9EB8-EF0D-4CF6-A222-547BEED43359}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8391525" y="13096875"/>
+            <a:ext cx="2508054" cy="963778"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val -51544"/>
+              <a:gd name="adj2" fmla="val 70585"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Apache</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>！リクエスト出したんだから、レスポンスをすぐに返さんかい！！！</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -609,80 +1232,251 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A39934E-D56B-4278-B2B9-5729874B5739}">
-  <dimension ref="B20:L36"/>
+  <dimension ref="B15:W64"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="B35" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="C22" t="s">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C37" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="B42" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B45" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="8"/>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="J47" s="9"/>
+      <c r="K47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="10"/>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="9"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="10"/>
+    </row>
+    <row r="49" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="9"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="10"/>
+    </row>
+    <row r="50" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J50" s="9"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="10"/>
+    </row>
+    <row r="51" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="9"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="10"/>
+    </row>
+    <row r="52" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="C23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="C25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="L30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="C32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="J52" s="9"/>
+      <c r="K52" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C33" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B36" t="s">
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="10"/>
+    </row>
+    <row r="53" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="J53" s="9"/>
+      <c r="K53" s="5" t="s">
         <v>15</v>
+      </c>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="10"/>
+    </row>
+    <row r="54" spans="2:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="11"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12"/>
+      <c r="R54" s="12"/>
+      <c r="S54" s="12"/>
+      <c r="T54" s="12"/>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="13"/>
+    </row>
+    <row r="55" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="2:23" x14ac:dyDescent="0.4">
+      <c r="H64" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -691,4 +1485,35 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FEF8AB1-17DA-4408-9712-FBB556897AB8}">
+  <dimension ref="B2:B6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>